--- a/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>JNVR</t>
   </si>
@@ -1045,8 +1045,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
@@ -1141,8 +1141,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
+      <c r="D23" s="3">
+        <v>-1600</v>
       </c>
       <c r="E23" s="3">
         <v>-400</v>
@@ -1237,8 +1237,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
+      <c r="D26" s="3">
+        <v>-1600</v>
       </c>
       <c r="E26" s="3">
         <v>-400</v>
@@ -1269,8 +1269,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
+      <c r="D27" s="3">
+        <v>-1600</v>
       </c>
       <c r="E27" s="3">
         <v>-400</v>
@@ -1429,8 +1429,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
@@ -1461,8 +1461,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="3">
+        <v>-1600</v>
       </c>
       <c r="E33" s="3">
         <v>-400</v>
@@ -1525,8 +1525,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
+      <c r="D35" s="3">
+        <v>-1600</v>
       </c>
       <c r="E35" s="3">
         <v>-400</v>
@@ -2789,8 +2789,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
+      <c r="D81" s="3">
+        <v>-1600</v>
       </c>
       <c r="E81" s="3">
         <v>-400</v>

--- a/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>JNVR</t>
   </si>
@@ -656,102 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>400</v>
+      </c>
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>500</v>
       </c>
       <c r="H8" s="3">
         <v>500</v>
       </c>
       <c r="I8" s="3">
+        <v>500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>500</v>
+      </c>
+      <c r="K8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
@@ -777,13 +790,19 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>400</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>5</v>
@@ -809,8 +828,14 @@
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +848,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -832,31 +859,37 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
         <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
       </c>
       <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>100</v>
       </c>
       <c r="L12" s="3">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="N12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +920,14 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,31 +958,37 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -951,8 +996,14 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +1013,86 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-400</v>
       </c>
       <c r="J18" s="3">
         <v>-600</v>
       </c>
       <c r="K18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,48 +1105,56 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1200</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
@@ -1104,8 +1177,14 @@
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,46 +1209,58 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-900</v>
       </c>
       <c r="L23" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1291,14 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1329,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-900</v>
       </c>
       <c r="L26" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-900</v>
       </c>
       <c r="L27" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1443,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1481,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1519,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1557,90 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-900</v>
       </c>
       <c r="L33" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1671,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-900</v>
       </c>
       <c r="L35" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1772,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1788,48 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F41" s="3">
         <v>5800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,8 +1860,14 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1696,7 +1881,7 @@
         <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -1705,16 +1890,22 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1745,20 +1936,26 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
@@ -1771,46 +1968,58 @@
       <c r="J45" s="3">
         <v>0</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F46" s="3">
         <v>6100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1841,8 +2050,14 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1867,22 +2082,28 @@
       <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K48" s="3">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
+        <v>100</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -1899,14 +2120,20 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2164,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,8 +2202,14 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1978,31 +2217,37 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2278,52 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F54" s="3">
         <v>6200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2336,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,8 +2352,10 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2102,7 +2363,7 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F57" s="3">
         <v>200</v>
@@ -2111,7 +2372,7 @@
         <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
@@ -2119,14 +2380,20 @@
       <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
+        <v>100</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2157,8 +2424,14 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2166,7 +2439,7 @@
         <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -2175,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
@@ -2183,22 +2456,28 @@
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E60" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="F60" s="3">
         <v>200</v>
@@ -2213,16 +2492,22 @@
         <v>200</v>
       </c>
       <c r="J60" s="3">
+        <v>200</v>
+      </c>
+      <c r="K60" s="3">
+        <v>200</v>
+      </c>
+      <c r="L60" s="3">
         <v>100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2253,40 +2538,52 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
+        <v>200</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2614,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2652,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2690,52 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E66" s="3">
         <v>900</v>
       </c>
       <c r="F66" s="3">
+        <v>200</v>
+      </c>
+      <c r="G66" s="3">
+        <v>900</v>
+      </c>
+      <c r="H66" s="3">
         <v>800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2000</v>
       </c>
       <c r="J66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2748,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2782,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2820,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2858,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,22 +2896,28 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-5500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-3900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-3300</v>
       </c>
       <c r="H72" s="3">
         <v>-3500</v>
@@ -2579,16 +2926,22 @@
         <v>-3300</v>
       </c>
       <c r="J72" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K72" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L72" s="3">
         <v>-2900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2972,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3010,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +3048,52 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F76" s="3">
         <v>6000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +3124,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-900</v>
       </c>
       <c r="L81" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,31 +3225,33 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -2862,8 +3259,14 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3297,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3335,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3373,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3411,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3449,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,8 +3507,10 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3100,8 +3541,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3579,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,8 +3617,14 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3173,22 +3632,22 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3196,8 +3655,14 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3675,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3709,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3747,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3785,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3823,52 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>4800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>200</v>
       </c>
       <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
+        <v>200</v>
+      </c>
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +3899,48 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>800</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-300</v>
       </c>
       <c r="H102" s="3">
         <v>-200</v>
       </c>
       <c r="I102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>JNVR</t>
   </si>
@@ -656,72 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -732,13 +736,13 @@
         <v>400</v>
       </c>
       <c r="F8" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G8" s="3">
         <v>600</v>
       </c>
       <c r="H8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I8" s="3">
         <v>500</v>
@@ -747,27 +751,30 @@
         <v>500</v>
       </c>
       <c r="K8" s="3">
+        <v>500</v>
+      </c>
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
@@ -796,16 +803,19 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
         <v>400</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
+      <c r="E10" s="3">
+        <v>400</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>5</v>
@@ -834,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -859,37 +873,40 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>100</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3">
         <v>100</v>
       </c>
       <c r="L12" s="3">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3">
         <v>200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
       </c>
       <c r="N12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,17 +984,20 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
@@ -990,8 +1013,8 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1002,8 +1025,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1100</v>
       </c>
       <c r="K17" s="3">
         <v>1100</v>
       </c>
       <c r="L17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-200</v>
       </c>
       <c r="H18" s="3">
         <v>-200</v>
       </c>
       <c r="I18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1140,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1116,49 +1150,52 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>400</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1183,8 +1220,11 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1215,43 +1255,46 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-900</v>
       </c>
       <c r="M23" s="3">
         <v>-900</v>
@@ -1259,8 +1302,11 @@
       <c r="N23" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1343,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,37 +1384,40 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-900</v>
       </c>
       <c r="M26" s="3">
         <v>-900</v>
@@ -1373,37 +1425,40 @@
       <c r="N26" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-900</v>
       </c>
       <c r="M27" s="3">
         <v>-900</v>
@@ -1411,8 +1466,11 @@
       <c r="N27" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1630,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1572,66 +1642,69 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-400</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-900</v>
       </c>
       <c r="M33" s="3">
         <v>-900</v>
@@ -1639,8 +1712,11 @@
       <c r="N33" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,37 +1753,40 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-900</v>
       </c>
       <c r="M35" s="3">
         <v>-900</v>
@@ -1715,51 +1794,57 @@
       <c r="N35" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1866,8 +1956,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1887,25 +1980,28 @@
         <v>100</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1942,8 +2038,11 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1954,11 +2053,11 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
@@ -1974,52 +2073,58 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2056,8 +2161,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2088,14 +2196,17 @@
       <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
+      <c r="M48" s="3">
+        <v>100</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2103,11 +2214,11 @@
         <v>1200</v>
       </c>
       <c r="E49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F49" s="3">
         <v>1300</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -2126,14 +2237,17 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,13 +2325,16 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2223,31 +2343,34 @@
         <v>0</v>
       </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
         <v>300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,8 +2484,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2363,10 +2494,10 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>500</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
@@ -2378,22 +2509,25 @@
         <v>200</v>
       </c>
       <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2430,8 +2564,11 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2445,14 +2582,14 @@
         <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
@@ -2462,14 +2599,17 @@
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
+      <c r="M59" s="3">
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2477,10 +2617,10 @@
         <v>300</v>
       </c>
       <c r="E60" s="3">
+        <v>300</v>
+      </c>
+      <c r="F60" s="3">
         <v>700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>200</v>
       </c>
       <c r="G60" s="3">
         <v>200</v>
@@ -2498,16 +2638,19 @@
         <v>200</v>
       </c>
       <c r="L60" s="3">
+        <v>200</v>
+      </c>
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2544,8 +2687,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2556,34 +2702,37 @@
         <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1800</v>
       </c>
       <c r="L62" s="3">
         <v>1800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
+      <c r="M62" s="3">
+        <v>1800</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,8 +2851,11 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2705,37 +2863,40 @@
         <v>500</v>
       </c>
       <c r="E66" s="3">
+        <v>500</v>
+      </c>
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>800</v>
       </c>
       <c r="I66" s="3">
         <v>800</v>
       </c>
       <c r="J66" s="3">
+        <v>800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1900</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E76" s="3">
         <v>5000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,80 +3319,86 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-900</v>
       </c>
       <c r="M81" s="3">
         <v>-900</v>
@@ -3211,8 +3406,11 @@
       <c r="N81" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,19 +3425,20 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
@@ -3253,8 +3452,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3265,8 +3464,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-200</v>
       </c>
       <c r="I89" s="3">
         <v>-200</v>
       </c>
       <c r="J89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,8 +3729,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3547,8 +3768,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,8 +3850,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3632,11 +3862,11 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>5</v>
       </c>
@@ -3649,8 +3879,8 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -3661,8 +3891,11 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,8 +4072,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3841,34 +4087,37 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>4800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4154,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-200</v>
       </c>
       <c r="K102" s="3">
         <v>-200</v>
       </c>
       <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>JNVR</t>
   </si>
@@ -656,81 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E8" s="3">
         <v>400</v>
@@ -739,13 +743,13 @@
         <v>400</v>
       </c>
       <c r="G8" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H8" s="3">
         <v>600</v>
       </c>
       <c r="I8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J8" s="3">
         <v>500</v>
@@ -754,19 +758,22 @@
         <v>500</v>
       </c>
       <c r="L8" s="3">
+        <v>500</v>
+      </c>
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -776,8 +783,8 @@
       <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>5</v>
@@ -806,31 +813,34 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="F10" s="3">
+        <v>400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>400</v>
+      </c>
+      <c r="H10" s="3">
+        <v>600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -876,37 +890,40 @@
         <v>200</v>
       </c>
       <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>100</v>
       </c>
       <c r="I12" s="3">
         <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3">
         <v>100</v>
       </c>
       <c r="M12" s="3">
+        <v>100</v>
+      </c>
+      <c r="N12" s="3">
         <v>200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>100</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,31 +963,34 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -987,37 +1007,40 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1100</v>
       </c>
       <c r="L17" s="3">
         <v>1100</v>
       </c>
       <c r="M17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-200</v>
       </c>
       <c r="I18" s="3">
         <v>-200</v>
       </c>
       <c r="J18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,16 +1174,17 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1159,54 +1193,57 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>400</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="H21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1223,8 +1260,11 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1258,46 +1298,49 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-900</v>
       </c>
       <c r="N23" s="3">
         <v>-900</v>
@@ -1305,31 +1348,34 @@
       <c r="O23" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,40 +1436,43 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-900</v>
       </c>
       <c r="N26" s="3">
         <v>-900</v>
@@ -1428,40 +1480,43 @@
       <c r="O26" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-900</v>
       </c>
       <c r="N27" s="3">
         <v>-900</v>
@@ -1469,8 +1524,11 @@
       <c r="O27" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,16 +1700,19 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1651,63 +1721,66 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-400</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-900</v>
       </c>
       <c r="N33" s="3">
         <v>-900</v>
@@ -1715,8 +1788,11 @@
       <c r="O33" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,40 +1832,43 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-900</v>
       </c>
       <c r="N35" s="3">
         <v>-900</v>
@@ -1797,54 +1876,60 @@
       <c r="O35" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>3200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,13 +2049,16 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>100</v>
@@ -1983,48 +2076,51 @@
         <v>100</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
+      <c r="N43" s="3">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2041,31 +2137,34 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2076,78 +2175,84 @@
       <c r="M45" s="3">
         <v>0</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E46" s="3">
         <v>3400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2164,8 +2269,11 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2199,29 +2307,32 @@
       <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
+      <c r="N48" s="3">
+        <v>100</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E49" s="3">
         <v>1200</v>
       </c>
       <c r="F49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G49" s="3">
         <v>1300</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -2240,14 +2351,17 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,17 +2445,20 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
@@ -2346,31 +2466,34 @@
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E54" s="3">
         <v>4800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,22 +2615,23 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
         <v>500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
@@ -2512,22 +2643,25 @@
         <v>200</v>
       </c>
       <c r="K57" s="3">
+        <v>200</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2538,19 +2672,19 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2567,13 +2701,16 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
         <v>100</v>
@@ -2584,14 +2721,14 @@
       <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -2602,28 +2739,31 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E60" s="3">
         <v>300</v>
       </c>
       <c r="F60" s="3">
+        <v>300</v>
+      </c>
+      <c r="G60" s="3">
         <v>700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>200</v>
       </c>
       <c r="H60" s="3">
         <v>200</v>
@@ -2641,16 +2781,19 @@
         <v>200</v>
       </c>
       <c r="M60" s="3">
+        <v>200</v>
+      </c>
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2690,8 +2833,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2705,34 +2851,37 @@
         <v>200</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
+        <v>200</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1800</v>
       </c>
       <c r="M62" s="3">
         <v>1800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
+      <c r="N62" s="3">
+        <v>1800</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,8 +3009,11 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2866,37 +3024,40 @@
         <v>500</v>
       </c>
       <c r="F66" s="3">
+        <v>500</v>
+      </c>
+      <c r="G66" s="3">
         <v>900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>800</v>
       </c>
       <c r="J66" s="3">
         <v>800</v>
       </c>
       <c r="K66" s="3">
+        <v>800</v>
+      </c>
+      <c r="L66" s="3">
         <v>1900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1900</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,86 +3511,92 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-900</v>
       </c>
       <c r="N81" s="3">
         <v>-900</v>
@@ -3409,8 +3604,11 @@
       <c r="O81" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,19 +3624,20 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
@@ -3455,8 +3654,8 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3467,8 +3666,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-200</v>
       </c>
       <c r="J89" s="3">
         <v>-200</v>
       </c>
       <c r="K89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +3950,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3750,11 +3971,11 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,8 +4080,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3865,13 +4095,13 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>5</v>
@@ -3882,8 +4112,8 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -3894,8 +4124,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,31 +4144,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,13 +4318,16 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -4090,57 +4336,60 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>4800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-200</v>
       </c>
       <c r="L102" s="3">
         <v>-200</v>
       </c>
       <c r="M102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JNVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>JNVR</t>
   </si>
@@ -656,80 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -737,7 +740,7 @@
         <v>600</v>
       </c>
       <c r="E8" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F8" s="3">
         <v>400</v>
@@ -746,13 +749,13 @@
         <v>400</v>
       </c>
       <c r="H8" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I8" s="3">
         <v>600</v>
       </c>
       <c r="J8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K8" s="3">
         <v>500</v>
@@ -761,19 +764,22 @@
         <v>500</v>
       </c>
       <c r="M8" s="3">
+        <v>500</v>
+      </c>
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -786,8 +792,8 @@
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>5</v>
@@ -816,8 +822,11 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -825,7 +834,7 @@
         <v>600</v>
       </c>
       <c r="E10" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F10" s="3">
         <v>400</v>
@@ -834,17 +843,17 @@
         <v>400</v>
       </c>
       <c r="H10" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I10" s="3">
         <v>600</v>
       </c>
       <c r="J10" s="3">
+        <v>600</v>
+      </c>
+      <c r="K10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -860,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -893,37 +906,40 @@
         <v>200</v>
       </c>
       <c r="G12" s="3">
+        <v>200</v>
+      </c>
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
       </c>
       <c r="J12" s="3">
         <v>100</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12" s="3">
         <v>100</v>
       </c>
       <c r="N12" s="3">
+        <v>100</v>
+      </c>
+      <c r="O12" s="3">
         <v>200</v>
-      </c>
-      <c r="O12" s="3">
-        <v>100</v>
       </c>
       <c r="P12" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,16 +982,19 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="E14" s="3">
+        <v>100</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -992,8 +1011,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1010,8 +1029,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1019,14 +1041,14 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1036,14 +1058,14 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1054,8 +1076,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1100</v>
       </c>
       <c r="M17" s="3">
         <v>1100</v>
       </c>
       <c r="N17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,13 +1207,14 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1196,31 +1229,34 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>400</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1228,26 +1264,26 @@
         <v>-400</v>
       </c>
       <c r="E21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1263,8 +1299,11 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1301,14 +1340,17 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1316,34 +1358,34 @@
         <v>-500</v>
       </c>
       <c r="E23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-900</v>
       </c>
       <c r="O23" s="3">
         <v>-900</v>
@@ -1351,8 +1393,11 @@
       <c r="P23" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1377,8 +1422,8 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1395,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,8 +1487,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1448,34 +1499,34 @@
         <v>-500</v>
       </c>
       <c r="E26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-900</v>
       </c>
       <c r="O26" s="3">
         <v>-900</v>
@@ -1483,8 +1534,11 @@
       <c r="P26" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1492,34 +1546,34 @@
         <v>-500</v>
       </c>
       <c r="E27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-900</v>
       </c>
       <c r="O27" s="3">
         <v>-900</v>
@@ -1527,8 +1581,11 @@
       <c r="P27" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,13 +1769,16 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1724,31 +1793,34 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-400</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1756,34 +1828,34 @@
         <v>-500</v>
       </c>
       <c r="E33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-900</v>
       </c>
       <c r="O33" s="3">
         <v>-900</v>
@@ -1791,8 +1863,11 @@
       <c r="P33" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,8 +1910,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1844,34 +1922,34 @@
         <v>-500</v>
       </c>
       <c r="E35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-900</v>
       </c>
       <c r="O35" s="3">
         <v>-900</v>
@@ -1879,57 +1957,63 @@
       <c r="P35" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2049,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,16 +2141,19 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
-      </c>
-      <c r="E43" s="3">
-        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -2079,25 +2171,28 @@
         <v>100</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2122,8 +2217,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2140,16 +2235,19 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
@@ -2166,8 +2264,8 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2178,67 +2276,73 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1700</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>200</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2254,8 +2358,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2272,13 +2376,16 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>100</v>
+      <c r="D48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
@@ -2310,32 +2417,35 @@
       <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
+      <c r="O48" s="3">
+        <v>100</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>1100</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1200</v>
       </c>
       <c r="F49" s="3">
         <v>1200</v>
       </c>
       <c r="G49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H49" s="3">
         <v>1300</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -2354,14 +2464,17 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,20 +2564,23 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
@@ -2475,25 +2594,28 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1900</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,25 +2745,26 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>200</v>
       </c>
       <c r="G57" s="3">
+        <v>200</v>
+      </c>
+      <c r="H57" s="3">
         <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>200</v>
@@ -2646,22 +2776,25 @@
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2672,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>100</v>
@@ -2681,14 +2814,14 @@
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2704,16 +2837,19 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
-      </c>
-      <c r="E59" s="3">
-        <v>100</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -2721,8 +2857,8 @@
       <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
+      <c r="H59" s="3">
+        <v>100</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
@@ -2730,8 +2866,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -2742,31 +2878,34 @@
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
+      <c r="O59" s="3">
+        <v>0</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>600</v>
+      </c>
+      <c r="E60" s="3">
         <v>400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>300</v>
       </c>
       <c r="F60" s="3">
         <v>300</v>
       </c>
       <c r="G60" s="3">
+        <v>300</v>
+      </c>
+      <c r="H60" s="3">
         <v>700</v>
-      </c>
-      <c r="H60" s="3">
-        <v>200</v>
       </c>
       <c r="I60" s="3">
         <v>200</v>
@@ -2784,16 +2923,19 @@
         <v>200</v>
       </c>
       <c r="N60" s="3">
+        <v>200</v>
+      </c>
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2836,13 +2978,16 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
         <v>200</v>
@@ -2853,35 +2998,38 @@
       <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="H62" s="3">
+        <v>200</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1800</v>
       </c>
       <c r="N62" s="3">
         <v>1800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
+      <c r="O62" s="3">
+        <v>1800</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,13 +3166,16 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E66" s="3">
         <v>500</v>
@@ -3027,37 +3184,40 @@
         <v>500</v>
       </c>
       <c r="G66" s="3">
+        <v>500</v>
+      </c>
+      <c r="H66" s="3">
         <v>900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>800</v>
       </c>
       <c r="K66" s="3">
         <v>800</v>
       </c>
       <c r="L66" s="3">
+        <v>800</v>
+      </c>
+      <c r="M66" s="3">
         <v>1900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3420,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>-8900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-100</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,57 +3702,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3572,34 +3766,34 @@
         <v>-500</v>
       </c>
       <c r="E81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-900</v>
       </c>
       <c r="O81" s="3">
         <v>-900</v>
@@ -3607,8 +3801,11 @@
       <c r="P81" s="3">
         <v>-900</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,16 +3822,17 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
@@ -3657,8 +3855,8 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3669,8 +3867,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-200</v>
       </c>
       <c r="K89" s="3">
         <v>-200</v>
       </c>
       <c r="L89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,13 +4170,14 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3971,14 +4191,14 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3995,8 +4215,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,13 +4309,16 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -4098,13 +4327,13 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>5</v>
@@ -4115,8 +4344,8 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4127,8 +4356,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,8 +4404,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,17 +4563,20 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -4339,34 +4584,37 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,8 +4639,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4409,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-200</v>
       </c>
       <c r="M102" s="3">
         <v>-200</v>
       </c>
       <c r="N102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
     </row>
